--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/27_Bietervergleich_und_Erloesallokation.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/27_Bietervergleich_und_Erloesallokation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtangebote" sheetId="1" r:id="R26a90af2e9ac4b0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verhandlung_Schwetzingen" sheetId="2" r:id="R66f46ba0d07846c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abzuege_Arbeitspapier" sheetId="3" r:id="R67f7b9672d4d4372"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtangebote" sheetId="1" r:id="R0974f9fe599e4e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verhandlung_Schwetzingen" sheetId="2" r:id="Rabe1b57c1264480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abzuege_Arbeitspapier" sheetId="3" r:id="Re52fe46d64094af1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/27_Bietervergleich_und_Erloesallokation.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/27_Bietervergleich_und_Erloesallokation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtangebote" sheetId="1" r:id="R0974f9fe599e4e91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verhandlung_Schwetzingen" sheetId="2" r:id="Rabe1b57c1264480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abzuege_Arbeitspapier" sheetId="3" r:id="Re52fe46d64094af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gesamtangebote" sheetId="1" r:id="Rc1f21b7015514a45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verhandlung_Schwetzingen" sheetId="2" r:id="R203cfcca590249bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abzuege_Arbeitspapier" sheetId="3" r:id="Rbd9eef9940fc4f5b"/>
   </x:sheets>
 </x:workbook>
 </file>
